--- a/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_54_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_54_EL.xlsx
@@ -662,13 +662,13 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="L2" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="M2" t="n">
         <v>11</v>
@@ -745,17 +745,17 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M3" t="n">
         <v>9</v>
@@ -904,17 +904,17 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -1335,7 +1335,7 @@
         <v>7</v>
       </c>
       <c r="T17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
@@ -1534,7 +1534,7 @@
         <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1730,7 +1730,7 @@
         <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -2122,13 +2122,13 @@
         <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X21" t="n">
         <v>6</v>
@@ -2315,16 +2315,16 @@
         <v>8</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V22" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
         <v>1</v>
@@ -3099,16 +3099,16 @@
         <v>18</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X26" t="n">
         <v>4</v>
@@ -3494,13 +3494,13 @@
         <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X28" t="n">
         <v>3</v>
@@ -3827,16 +3827,16 @@
         <v>87</v>
       </c>
       <c r="T30" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="V30" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="W30" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="X30" t="n">
         <v>19</v>
@@ -4298,10 +4298,10 @@
         <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X35" t="n">
         <v>1</v>
@@ -4684,10 +4684,10 @@
         <v>14</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V37" t="n">
         <v>0</v>
@@ -4883,7 +4883,7 @@
         <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V38" t="n">
         <v>0</v>
@@ -5082,10 +5082,10 @@
         <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X39" t="n">
         <v>1</v>
@@ -5272,16 +5272,16 @@
         <v>23</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X40" t="n">
         <v>2</v>
@@ -6252,7 +6252,7 @@
         <v>9</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U45" t="n">
         <v>0</v>
@@ -6454,10 +6454,10 @@
         <v>0</v>
       </c>
       <c r="V46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X46" t="n">
         <v>1</v>
@@ -6784,16 +6784,16 @@
         <v>99</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="V48" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="W48" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="X48" t="n">
         <v>18</v>

--- a/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_54_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_54_EL.xlsx
@@ -674,10 +674,10 @@
         <v>11</v>
       </c>
       <c r="N2" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="O2" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="P2" t="n">
         <v>14</v>
@@ -705,7 +705,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>95.00</t>
+          <t>75.00</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -730,7 +730,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -833,10 +833,10 @@
         <v>9</v>
       </c>
       <c r="N3" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="O3" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="P3" t="n">
         <v>13</v>
@@ -864,7 +864,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>90.00</t>
+          <t>77.78</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -1347,14 +1347,14 @@
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA17" t="n">
@@ -1739,14 +1739,14 @@
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA19" t="n">
@@ -2131,10 +2131,10 @@
         <v>1</v>
       </c>
       <c r="X21" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Y21" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
@@ -2327,14 +2327,14 @@
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA22" t="n">
@@ -3111,10 +3111,10 @@
         <v>3</v>
       </c>
       <c r="X26" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y26" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
@@ -3503,14 +3503,14 @@
         <v>3</v>
       </c>
       <c r="X28" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA28" t="n">
@@ -3839,14 +3839,14 @@
         <v>7</v>
       </c>
       <c r="X30" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="Y30" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>95.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="AA30" t="n">
@@ -4500,14 +4500,14 @@
         <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA36" t="n">
@@ -4696,10 +4696,10 @@
         <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y37" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
@@ -4892,14 +4892,14 @@
         <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA38" t="n">
@@ -5284,14 +5284,14 @@
         <v>2</v>
       </c>
       <c r="X40" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y40" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AA40" t="n">
@@ -6264,10 +6264,10 @@
         <v>0</v>
       </c>
       <c r="X45" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y45" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
@@ -6460,14 +6460,14 @@
         <v>1</v>
       </c>
       <c r="X46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA46" t="n">
@@ -6796,14 +6796,14 @@
         <v>6</v>
       </c>
       <c r="X48" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="Y48" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>90.0%</t>
+          <t>77.8%</t>
         </is>
       </c>
       <c r="AA48" t="n">
